--- a/output/北塩原村_報告書の修正方針と計画への影響.xlsx
+++ b/output/北塩原村_報告書の修正方針と計画への影響.xlsx
@@ -2940,7 +2940,7 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>P881</t>
+          <t>P883</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">

--- a/output/北塩原村_報告書の修正方針と計画への影響.xlsx
+++ b/output/北塩原村_報告書の修正方針と計画への影響.xlsx
@@ -2940,7 +2940,7 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>P883</t>
+          <t>P887</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">

--- a/output/北塩原村_報告書の修正方針と計画への影響.xlsx
+++ b/output/北塩原村_報告書の修正方針と計画への影響.xlsx
@@ -2940,7 +2940,7 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>P887</t>
+          <t>P889</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>P569</t>
+          <t>P570</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">

--- a/output/北塩原村_報告書の修正方針と計画への影響.xlsx
+++ b/output/北塩原村_報告書の修正方針と計画への影響.xlsx
@@ -2940,7 +2940,7 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>P889</t>
+          <t>P890</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
